--- a/healthcare_forms/005_covid_19_symptom_checklist--healthcare_forms.xlsx
+++ b/healthcare_forms/005_covid_19_symptom_checklist--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>sore_throat_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Sore Throat 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>muscle_pain</t>
+          <t>muscle_pain_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muscle pain</t>
+          <t>Muscle Pain 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>runny_nose_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Runny nose</t>
+          <t>Runny Nose 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss_of_taste_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loss of taste</t>
+          <t>Loss Of Taste 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>loss_of_smell_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loss of smell</t>
+          <t>Loss Of Smell 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sore_throat_choices</t>
+          <t>sore_throat_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sore_throat_choices</t>
+          <t>sore_throat_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>muscle_pain_choices</t>
+          <t>muscle_pain_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>muscle_pain_choices</t>
+          <t>muscle_pain_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1878,7 +1878,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>runny_nose_choices</t>
+          <t>runny_nose_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>runny_nose_choices</t>
+          <t>runny_nose_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>loss_of_taste_choices</t>
+          <t>loss_of_taste_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1929,7 +1929,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>loss_of_taste_choices</t>
+          <t>loss_of_taste_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>loss_of_smell_choices</t>
+          <t>loss_of_smell_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>loss_of_smell_choices</t>
+          <t>loss_of_smell_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
